--- a/artfynd/A 42231-2024 artfynd.xlsx
+++ b/artfynd/A 42231-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,7 +2049,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88455728</v>
+        <v>88455727</v>
       </c>
       <c r="B12" t="n">
         <v>42702</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637690.7963411163</v>
+        <v>637692.935703186</v>
       </c>
       <c r="R12" t="n">
-        <v>6714359.17727326</v>
+        <v>6714354.826273442</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88455727</v>
+        <v>88767298</v>
       </c>
       <c r="B13" t="n">
-        <v>42702</v>
+        <v>95519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2201,60 +2201,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100942</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östanån, Upl</t>
+          <t>skog N om Östanå KLG, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>637692.935703186</v>
+        <v>637655.871972174</v>
       </c>
       <c r="R13" t="n">
-        <v>6714354.826273442</v>
+        <v>6714602.124717766</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2278,7 +2268,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
+          <t>2020-01-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2288,17 +2278,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
+          <t>2020-01-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Utanför Natura 2000-området</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2313,26 +2298,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88767298</v>
+        <v>96911961</v>
       </c>
       <c r="B14" t="n">
-        <v>95519</v>
+        <v>42702</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2341,50 +2322,62 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100942</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>skog N om Östanå KLG, Upl</t>
+          <t>Östanån, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637655.871972174</v>
+        <v>637584.2775394894</v>
       </c>
       <c r="R14" t="n">
-        <v>6714602.124717766</v>
+        <v>6714396.976689922</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2408,7 +2401,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-01-28</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2418,7 +2411,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-01-28</t>
+          <t>2021-08-21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -2432,25 +2425,30 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96911961</v>
+        <v>96911932</v>
       </c>
       <c r="B15" t="n">
         <v>42702</v>
@@ -2511,10 +2509,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637584.2775394894</v>
+        <v>637682.5534936595</v>
       </c>
       <c r="R15" t="n">
-        <v>6714396.976689922</v>
+        <v>6714355.41502798</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2588,7 +2586,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96911932</v>
+        <v>96911936</v>
       </c>
       <c r="B16" t="n">
         <v>42702</v>
@@ -2649,10 +2647,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>637682.5534936595</v>
+        <v>637663.5530480875</v>
       </c>
       <c r="R16" t="n">
-        <v>6714355.41502798</v>
+        <v>6714362.077631126</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2726,7 +2724,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96911936</v>
+        <v>96911935</v>
       </c>
       <c r="B17" t="n">
         <v>42702</v>
@@ -2787,10 +2785,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637663.5530480875</v>
+        <v>637664.8431683906</v>
       </c>
       <c r="R17" t="n">
-        <v>6714362.077631126</v>
+        <v>6714367.052030294</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2864,7 +2862,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96911935</v>
+        <v>96911954</v>
       </c>
       <c r="B18" t="n">
         <v>42702</v>
@@ -2925,10 +2923,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>637664.8431683906</v>
+        <v>637604.3003548346</v>
       </c>
       <c r="R18" t="n">
-        <v>6714367.052030294</v>
+        <v>6714389.367739137</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3002,7 +3000,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96911954</v>
+        <v>96911930</v>
       </c>
       <c r="B19" t="n">
         <v>42702</v>
@@ -3063,10 +3061,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637604.3003548346</v>
+        <v>637687.6484697075</v>
       </c>
       <c r="R19" t="n">
-        <v>6714389.367739137</v>
+        <v>6714351.17683167</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3140,7 +3138,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96911934</v>
+        <v>96911956</v>
       </c>
       <c r="B20" t="n">
         <v>42702</v>
@@ -3201,10 +3199,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>637664.8056311789</v>
+        <v>637599.3743714294</v>
       </c>
       <c r="R20" t="n">
-        <v>6714368.035629855</v>
+        <v>6714389.179832817</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3278,10 +3276,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96911930</v>
+        <v>96940370</v>
       </c>
       <c r="B21" t="n">
-        <v>42702</v>
+        <v>101680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3290,62 +3288,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100942</v>
+        <v>222412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östanån, Upl</t>
+          <t>Östanå ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637687.6484697075</v>
+        <v>637592.5398339895</v>
       </c>
       <c r="R21" t="n">
-        <v>6714351.17683167</v>
+        <v>6714451.960158829</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3369,7 +3355,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3379,7 +3365,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -3387,39 +3373,39 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>örtbarrskog 80 år</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96911956</v>
+        <v>96940380</v>
       </c>
       <c r="B22" t="n">
-        <v>42702</v>
+        <v>101680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3428,62 +3414,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100942</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östanån, Upl</t>
+          <t>Norr om Östanå ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637599.3743714294</v>
+        <v>637566.2966595029</v>
       </c>
       <c r="R22" t="n">
-        <v>6714389.179832817</v>
+        <v>6715036.498750668</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3507,7 +3481,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3517,7 +3491,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021-04-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3525,36 +3499,36 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>inom 50m, örtbarrskog 80 år</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96940370</v>
+        <v>96940369</v>
       </c>
       <c r="B23" t="n">
         <v>101680</v>
@@ -3599,14 +3573,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östanå ledningsgata, Upl</t>
+          <t>Norr om Östanå ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>637592.5398339895</v>
+        <v>637620.5339190547</v>
       </c>
       <c r="R23" t="n">
-        <v>6714451.960158829</v>
+        <v>6714946.483491838</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3680,7 +3654,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96940380</v>
+        <v>96940374</v>
       </c>
       <c r="B24" t="n">
         <v>101680</v>
@@ -3715,7 +3689,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3729,10 +3703,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>637566.2966595029</v>
+        <v>637613.9949856387</v>
       </c>
       <c r="R24" t="n">
-        <v>6715036.498750668</v>
+        <v>6714833.464161985</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3779,7 +3753,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>inom 50m, örtbarrskog 80 år</t>
+          <t>örtbarrskog 120 år</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3806,10 +3780,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96940369</v>
+        <v>96940597</v>
       </c>
       <c r="B25" t="n">
-        <v>101680</v>
+        <v>96355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3822,26 +3796,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3855,10 +3829,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>637620.5339190547</v>
+        <v>637663.7580239639</v>
       </c>
       <c r="R25" t="n">
-        <v>6714946.483491838</v>
+        <v>6714989.990066303</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3885,7 +3859,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3895,7 +3869,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3905,7 +3879,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>örtbarrskog 80 år</t>
+          <t>inom 30m</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3932,7 +3906,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96940374</v>
+        <v>96940368</v>
       </c>
       <c r="B26" t="n">
         <v>101680</v>
@@ -3967,7 +3941,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3981,10 +3955,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>637613.9949856387</v>
+        <v>637654.4576378858</v>
       </c>
       <c r="R26" t="n">
-        <v>6714833.464161985</v>
+        <v>6714884.745628751</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4031,7 +4005,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>örtbarrskog 120 år</t>
+          <t>örtbarrskog 80 år</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4058,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96940597</v>
+        <v>104592183</v>
       </c>
       <c r="B27" t="n">
-        <v>96355</v>
+        <v>42702</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4070,50 +4044,62 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219862</v>
+        <v>100942</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norr om Östanå ledningsgata, Upl</t>
+          <t>Östanån, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>637663.7580239639</v>
+        <v>637692.9920204466</v>
       </c>
       <c r="R27" t="n">
-        <v>6714989.990066303</v>
+        <v>6714353.350868474</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4137,7 +4123,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -4147,7 +4133,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -4157,7 +4143,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>inom 30m</t>
+          <t>Slåtteryta väster 0,58 ha</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4166,28 +4152,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96940368</v>
+        <v>104592181</v>
       </c>
       <c r="B28" t="n">
-        <v>101680</v>
+        <v>42702</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4196,50 +4187,62 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222412</v>
+        <v>100942</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norr om Östanå ledningsgata, Upl</t>
+          <t>Östanån, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>637654.4576378858</v>
+        <v>637669.6565674597</v>
       </c>
       <c r="R28" t="n">
-        <v>6714884.745628751</v>
+        <v>6714370.190823439</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4263,7 +4266,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -4273,7 +4276,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-04-26</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -4281,36 +4284,36 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>örtbarrskog 80 år</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104592183</v>
+        <v>104592172</v>
       </c>
       <c r="B29" t="n">
         <v>42702</v>
@@ -4371,10 +4374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>637692.9920204466</v>
+        <v>637597.3289402374</v>
       </c>
       <c r="R29" t="n">
-        <v>6714353.350868474</v>
+        <v>6714391.071858598</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4453,7 +4456,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104592181</v>
+        <v>104592185</v>
       </c>
       <c r="B30" t="n">
         <v>42702</v>
@@ -4514,10 +4517,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>637669.6565674597</v>
+        <v>637697.8429619774</v>
       </c>
       <c r="R30" t="n">
-        <v>6714370.190823439</v>
+        <v>6714355.506108476</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4560,6 +4563,11 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Slåtteryta väster 0,58 ha</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4591,7 +4599,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104592172</v>
+        <v>104592186</v>
       </c>
       <c r="B31" t="n">
         <v>42702</v>
@@ -4652,10 +4660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>637597.3289402374</v>
+        <v>637697.9931467361</v>
       </c>
       <c r="R31" t="n">
-        <v>6714391.071858598</v>
+        <v>6714351.571694572</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4734,7 +4742,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104592185</v>
+        <v>104592190</v>
       </c>
       <c r="B32" t="n">
         <v>42702</v>
@@ -4795,10 +4803,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>637697.8429619774</v>
+        <v>637720.193435949</v>
       </c>
       <c r="R32" t="n">
-        <v>6714355.506108476</v>
+        <v>6714338.628642398</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4877,7 +4885,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104592186</v>
+        <v>104592171</v>
       </c>
       <c r="B33" t="n">
         <v>42702</v>
@@ -4938,10 +4946,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>637697.9931467361</v>
+        <v>637598.2390981178</v>
       </c>
       <c r="R33" t="n">
-        <v>6714351.571694572</v>
+        <v>6714393.076624111</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5020,7 +5028,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104592190</v>
+        <v>104592182</v>
       </c>
       <c r="B34" t="n">
         <v>42702</v>
@@ -5081,10 +5089,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>637720.193435949</v>
+        <v>637682.9334703683</v>
       </c>
       <c r="R34" t="n">
-        <v>6714338.628642398</v>
+        <v>6714358.384637145</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5163,7 +5171,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104592171</v>
+        <v>104592173</v>
       </c>
       <c r="B35" t="n">
         <v>42702</v>
@@ -5198,7 +5206,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5224,10 +5232,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>637598.2390981178</v>
+        <v>637602.2174008004</v>
       </c>
       <c r="R35" t="n">
-        <v>6714393.076624111</v>
+        <v>6714392.243354933</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -5306,7 +5314,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>104592182</v>
+        <v>104592184</v>
       </c>
       <c r="B36" t="n">
         <v>42702</v>
@@ -5367,10 +5375,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>637682.9334703683</v>
+        <v>637691.0216068393</v>
       </c>
       <c r="R36" t="n">
-        <v>6714358.384637145</v>
+        <v>6714353.275656923</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5449,10 +5457,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>104592173</v>
+        <v>104729146</v>
       </c>
       <c r="B37" t="n">
-        <v>42702</v>
+        <v>101120</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5461,62 +5469,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100942</v>
+        <v>222002</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Östanån, Upl</t>
+          <t>skog N om Östanå KLG, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>637602.2174008004</v>
+        <v>637611.7787709348</v>
       </c>
       <c r="R37" t="n">
-        <v>6714392.243354933</v>
+        <v>6714426.098758964</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5540,7 +5536,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -5550,7 +5546,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5558,44 +5554,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Slåtteryta väster 0,58 ha</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>104592184</v>
+        <v>104729479</v>
       </c>
       <c r="B38" t="n">
-        <v>42702</v>
+        <v>96239</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5604,62 +5590,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100942</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Euphydryas aurinia</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Rottemburg, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Östanån, Upl</t>
+          <t>Söder om väg 76 och Frostbo- området, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>637691.0216068393</v>
+        <v>637684.3112566014</v>
       </c>
       <c r="R38" t="n">
-        <v>6714353.275656923</v>
+        <v>6715045.926613069</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5683,7 +5657,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -5693,7 +5667,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5703,7 +5677,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Slåtteryta väster 0,58 ha</t>
+          <t>ny lokal</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5712,33 +5686,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
+          <t>Tommy Löfgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
-        </is>
-      </c>
+          <t>Tommy Löfgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>104729146</v>
+        <v>81678894</v>
       </c>
       <c r="B39" t="n">
-        <v>101120</v>
+        <v>96239</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5751,16 +5720,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222002</v>
+        <v>504</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5770,24 +5739,24 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>skog N om Östanå KLG, Upl</t>
+          <t>S om 76:an, V om Lämpesbo, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>637611.7787709348</v>
+        <v>637731.0423688494</v>
       </c>
       <c r="R39" t="n">
-        <v>6714426.098758964</v>
+        <v>6714932.974266094</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5814,7 +5783,7 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -5824,7 +5793,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2019-05-24</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
@@ -5856,7 +5825,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>104729479</v>
+        <v>96940692</v>
       </c>
       <c r="B40" t="n">
         <v>96239</v>
@@ -5891,7 +5860,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5901,14 +5870,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söder om väg 76 och Frostbo- området, Upl</t>
+          <t>Norr om Östanå ledningsgata, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>637684.3112566014</v>
+        <v>637720.5910118197</v>
       </c>
       <c r="R40" t="n">
-        <v>6715045.926613069</v>
+        <v>6714948.333199995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5935,7 +5904,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5945,7 +5914,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
@@ -5955,7 +5924,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ny lokal</t>
+          <t>36 blommar, varav en gul ?</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5982,10 +5951,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>81678894</v>
+        <v>113236031</v>
       </c>
       <c r="B41" t="n">
-        <v>96239</v>
+        <v>42894</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5994,50 +5963,62 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>504</v>
+        <v>100942</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>S om 76:an, V om Lämpesbo, Upl</t>
+          <t>Östanån, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>637731.0423688494</v>
+        <v>637602</v>
       </c>
       <c r="R41" t="n">
-        <v>6714932.974266094</v>
+        <v>6714390</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -6061,22 +6042,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-05-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6085,28 +6056,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>96940692</v>
+        <v>113236034</v>
       </c>
       <c r="B42" t="n">
-        <v>96239</v>
+        <v>42894</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6115,50 +6091,62 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>504</v>
+        <v>100942</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Euphydryas aurinia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rottemburg, 1775)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Norr om Östanå ledningsgata, Upl</t>
+          <t>Östanån, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>637720.5910118197</v>
+        <v>637595</v>
       </c>
       <c r="R42" t="n">
-        <v>6714948.333199995</v>
+        <v>6714394</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6182,27 +6170,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>36 blommar, varav en gul ?</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6211,25 +6184,30 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
+          <t>Pavel Bina</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tommy Löfgren</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Pavel Bina</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>113236031</v>
+        <v>113236037</v>
       </c>
       <c r="B43" t="n">
         <v>42894</v>
@@ -6290,10 +6268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>637602</v>
+        <v>637591</v>
       </c>
       <c r="R43" t="n">
-        <v>6714390</v>
+        <v>6714394</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6357,10 +6335,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>113236034</v>
+        <v>120775823</v>
       </c>
       <c r="B44" t="n">
-        <v>42894</v>
+        <v>42959</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6418,10 +6396,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>637595</v>
+        <v>637697</v>
       </c>
       <c r="R44" t="n">
-        <v>6714394</v>
+        <v>6714354</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6448,12 +6426,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6479,16 +6457,16 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>113236037</v>
+        <v>120775820</v>
       </c>
       <c r="B45" t="n">
-        <v>42894</v>
+        <v>42959</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6546,10 +6524,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>637591</v>
+        <v>637666</v>
       </c>
       <c r="R45" t="n">
-        <v>6714394</v>
+        <v>6714364</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6576,12 +6554,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6607,13 +6585,13 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
+          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120775823</v>
+        <v>120775822</v>
       </c>
       <c r="B46" t="n">
         <v>42959</v>
@@ -6674,10 +6652,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>637697</v>
+        <v>637696</v>
       </c>
       <c r="R46" t="n">
-        <v>6714354</v>
+        <v>6714355</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6741,7 +6719,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120775820</v>
+        <v>120775821</v>
       </c>
       <c r="B47" t="n">
         <v>42959</v>
@@ -6802,10 +6780,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>637666</v>
+        <v>637687</v>
       </c>
       <c r="R47" t="n">
-        <v>6714364</v>
+        <v>6714353</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6862,262 +6840,6 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr">
-        <is>
-          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>120775822</v>
-      </c>
-      <c r="B48" t="n">
-        <v>42959</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100942</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Väddnätfjäril</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Euphydryas aurinia</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Rottemburg, 1775)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Östanån, Upl</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>637696</v>
-      </c>
-      <c r="R48" t="n">
-        <v>6714355</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>120775821</v>
-      </c>
-      <c r="B49" t="n">
-        <v>42959</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100942</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Väddnätfjäril</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Euphydryas aurinia</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Rottemburg, 1775)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>kolonier</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Östanån, Upl</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>637687</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6714353</v>
-      </c>
-      <c r="S49" t="n">
-        <v>5</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Västland</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Pavel Bina</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
         <is>
           <t>ÅGP väddnätfjäril, C-län, Biogeografisk uppföljning av fjärilar</t>
         </is>
